--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -479,13 +479,13 @@
       <c r="C1" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n">
         <v>1</v>
       </c>
@@ -500,10 +500,10 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>0.25</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>0.5</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.75</v>
@@ -542,10 +542,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -561,12 +565,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -586,12 +590,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -611,7 +615,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -628,7 +636,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -647,10 +659,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -666,12 +682,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -691,12 +707,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -722,10 +738,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -741,12 +761,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -766,12 +786,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -791,7 +811,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -808,7 +832,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -827,10 +855,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
     </row>
@@ -846,12 +878,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -877,10 +909,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -896,12 +932,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -921,12 +957,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -946,7 +982,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -963,7 +1003,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -980,12 +1024,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1011,10 +1055,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -1030,12 +1078,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1055,12 +1103,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1080,7 +1128,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1116,10 +1168,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1135,12 +1191,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1160,12 +1216,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1191,12 +1247,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1218,12 +1274,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1243,12 +1299,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1268,12 +1324,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1289,12 +1345,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1312,12 +1368,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1339,15 +1395,15 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1364,12 +1420,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1395,12 +1451,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1418,12 +1474,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1443,12 +1499,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1468,12 +1524,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
     </row>
@@ -1489,7 +1545,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1506,12 +1566,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1531,12 +1591,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1562,10 +1622,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
     </row>
@@ -1581,12 +1645,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1606,12 +1670,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1631,7 +1695,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -1648,7 +1716,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
@@ -1670,7 +1742,11 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1686,12 +1762,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1728,12 +1804,12 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1749,12 +1825,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1774,12 +1850,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1799,7 +1875,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -1816,7 +1896,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -1833,12 +1917,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1854,12 +1938,12 @@
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1885,10 +1969,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
     </row>
@@ -1904,12 +1992,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1929,12 +2017,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -1954,7 +2042,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
@@ -1971,7 +2063,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -1990,10 +2086,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
     </row>
@@ -2009,12 +2109,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2034,12 +2134,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2065,10 +2165,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
     </row>
@@ -2084,12 +2188,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2109,12 +2213,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2134,7 +2238,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2151,7 +2259,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
@@ -2168,12 +2280,12 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2193,12 +2305,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2222,12 +2334,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2247,12 +2359,12 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>[0]</t>
@@ -2265,8 +2377,8 @@
     <mergeCell ref="A71:A77"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A12:A18"/>
+    <mergeCell ref="C1:D1"/>
     <mergeCell ref="A56:A62"/>
-    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A48:A55"/>
     <mergeCell ref="A78:A79"/>
     <mergeCell ref="A25:A32"/>

--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -63,6 +63,13 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -467,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,15 +487,17 @@
         <v>0.1</v>
       </c>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
@@ -503,14 +512,26 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>0.25</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0.75</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>0.5</v>
       </c>
+      <c r="H2" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -537,21 +558,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -570,13 +619,17 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -587,21 +640,49 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -612,17 +693,49 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -633,17 +746,49 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -654,21 +799,49 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -679,21 +852,49 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -704,21 +905,49 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -733,21 +962,49 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -766,13 +1023,17 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -783,21 +1044,49 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -808,17 +1097,49 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -829,17 +1150,49 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -850,21 +1203,49 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 2, 3]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[0, 4]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -875,81 +1256,141 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>TREC</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>ADB</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>[0, 1, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -962,303 +1403,591 @@
           <t>[0]</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>ADB</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 2, 3]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[0, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1266,120 +1995,244 @@
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1387,943 +2240,1959 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>[0, 2, 3]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[0, 2]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[0, 2, 4]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n"/>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>[0, 2]</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n"/>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[1, 2]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n"/>
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>[0, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>[0, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>[2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>[2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 4]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>[2, 4]</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n"/>
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
           <t>ab</t>
@@ -2331,21 +4200,49 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
@@ -2356,36 +4253,128 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A71:A77"/>
+  <mergeCells count="14">
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A35:A42"/>
     <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A48:A55"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A65:A72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A27:A34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -823,12 +823,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2203,7 +2203,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -2642,14 +2646,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>[0, 1, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>[0, 3, 4]</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>[0, 3]</t>
@@ -2682,7 +2686,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2739,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3123,14 +3127,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>[0, 1, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>[0, 3, 4]</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[0, 3]</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>[0, 3]</t>
@@ -3161,7 +3165,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
@@ -3547,12 +3555,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3640,7 +3648,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4024,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4444,12 +4452,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4482,7 +4490,11 @@
           <t>[0, 3]</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[0, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
@@ -4533,7 +4545,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4933,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">

--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,47 +823,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1304,47 +1304,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1466,22 +1466,46 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1761,47 +1785,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1833,7 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1862,93 +1886,117 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
           <t>clap</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Yahoo</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>ADB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2001,7 +2049,7 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2054,7 +2102,7 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2107,7 +2155,7 @@
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2160,52 +2208,52 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2261,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2266,7 +2314,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2319,117 +2367,117 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
           <t>clap</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>banking</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>ADB</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2482,7 +2530,7 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2535,7 +2583,7 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2588,7 +2636,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2641,52 +2689,52 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2742,7 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2747,7 +2795,7 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2800,117 +2848,117 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
           <t>clap</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>clinc</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>ADB</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2963,7 +3011,7 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3016,7 +3064,7 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3069,7 +3117,7 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3122,52 +3170,52 @@
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3223,7 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3228,7 +3276,7 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3278,14 +3326,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3338,7 +3382,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3388,30 +3432,30 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n"/>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3444,7 +3488,7 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3497,7 +3541,7 @@
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3550,52 +3594,52 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3647,7 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3656,7 +3700,7 @@
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3709,12 +3753,12 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3759,19 +3803,27 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -3807,7 +3859,7 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3857,10 +3909,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n"/>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3913,7 +3969,7 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3966,7 +4022,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4019,52 +4075,52 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4128,7 @@
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4125,7 +4181,7 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4175,14 +4231,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4235,7 +4287,7 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4288,7 +4340,7 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4338,27 +4390,19 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n"/>
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -4394,7 +4438,7 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4447,52 +4491,52 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4544,7 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4553,7 +4597,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4606,7 +4650,7 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4656,21 +4700,13 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -4678,7 +4714,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4693,7 +4729,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4716,7 +4752,7 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4769,7 +4805,7 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4819,10 +4855,14 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n"/>
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4875,7 +4915,7 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4928,52 +4968,52 @@
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4981,7 +5021,7 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5034,7 +5074,7 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5084,83 +5124,1196 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>PLM_OOD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n"/>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
           <t>clap</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n"/>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n"/>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n"/>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n"/>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>PLM_OOD</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n"/>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n"/>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n"/>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>PLM_OOD</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A13:A21"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A48:A55"/>
+    <mergeCell ref="A76:A84"/>
+    <mergeCell ref="A94:A102"/>
+    <mergeCell ref="A103:A111"/>
+    <mergeCell ref="A22:A30"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A4:A12"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="A39:A47"/>
-    <mergeCell ref="A65:A72"/>
-    <mergeCell ref="A73:A81"/>
-    <mergeCell ref="A82:A89"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A31:A39"/>
+    <mergeCell ref="A49:A57"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A85:A93"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A67:A75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -679,32 +679,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3442,20 +3442,24 @@
           <t>ADB</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3758,7 +3762,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4400,9 +4404,21 @@
           <t>ADB</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -4706,7 +4722,11 @@
           <t>SCL</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -4714,7 +4734,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4729,7 +4749,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">

--- a/results/openset_progress.xlsx
+++ b/results/openset_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,7 +818,7 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,7 +871,7 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +924,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -977,7 +977,7 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1027,14 +1027,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DBPedia</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1087,7 +1083,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1140,7 +1136,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1193,7 +1189,7 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1246,7 +1242,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1299,7 +1295,7 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1352,7 +1348,7 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1405,7 +1401,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1455,10 +1451,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n"/>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1508,19 +1508,15 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>TREC</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1568,7 +1564,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1621,7 +1617,7 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1674,7 +1670,7 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1727,7 +1723,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1780,7 +1776,7 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1833,7 +1829,7 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1886,7 +1882,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1939,7 +1935,7 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1989,14 +1985,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2049,7 +2041,7 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2102,7 +2094,7 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2155,7 +2147,7 @@
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2208,7 +2200,7 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2261,7 +2253,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2314,7 +2306,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2364,10 +2356,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n"/>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2420,7 +2416,7 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2470,14 +2466,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2530,7 +2522,7 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2583,7 +2575,7 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2636,7 +2628,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2689,7 +2681,7 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2742,7 +2734,7 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2795,7 +2787,7 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2848,7 +2840,7 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2901,7 +2893,7 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2951,14 +2943,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3011,7 +2999,7 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3064,7 +3052,7 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3117,7 +3105,7 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3170,7 +3158,7 @@
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3223,7 +3211,7 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3273,10 +3261,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3329,7 +3321,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3382,7 +3374,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3432,14 +3424,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>ecdt</t>
-        </is>
-      </c>
+      <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3449,7 +3437,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3492,7 +3480,7 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3545,7 +3533,7 @@
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3598,7 +3586,7 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3651,7 +3639,7 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3704,7 +3692,7 @@
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3757,7 +3745,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3810,7 +3798,7 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3863,7 +3851,7 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3913,14 +3901,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3973,7 +3957,7 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4026,7 +4010,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4079,7 +4063,7 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4132,7 +4116,7 @@
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4182,10 +4166,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n"/>
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4238,7 +4226,7 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4291,7 +4279,7 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4344,7 +4332,7 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4394,14 +4382,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4454,7 +4438,7 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4507,7 +4491,7 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4560,7 +4544,7 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4613,7 +4597,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4666,7 +4650,7 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4719,7 +4703,7 @@
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4772,7 +4756,7 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4825,7 +4809,7 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4875,14 +4859,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4935,7 +4915,7 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4988,7 +4968,7 @@
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5041,7 +5021,7 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5091,10 +5071,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n"/>
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5147,7 +5131,7 @@
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5200,7 +5184,7 @@
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5253,7 +5237,7 @@
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5306,7 +5290,7 @@
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5356,14 +5340,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>Llama3.1-8B-EnergyBased</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5416,7 +5396,7 @@
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>Llama3.1-8B-Entropy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5469,7 +5449,7 @@
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>Llama3.1-8B-KLMatching</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5522,7 +5502,7 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>Llama3.1-8B-LogitNorm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5575,7 +5555,7 @@
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>Llama3.1-8B-Mahalanobis</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5628,7 +5608,7 @@
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>Llama3.1-8B-MaxLogit</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5681,7 +5661,7 @@
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>Llama3.1-8B-MaxSoftmax</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5734,7 +5714,7 @@
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Llama3.1-8B-OpenMax</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5787,7 +5767,7 @@
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>Llama3.1-8B-TemperatureScaling</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5837,14 +5817,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5897,7 +5873,7 @@
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5950,7 +5926,7 @@
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6000,10 +5976,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n"/>
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6056,7 +6036,7 @@
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6109,7 +6089,7 @@
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>PLM_OOD</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6162,7 +6142,7 @@
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6215,7 +6195,7 @@
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6268,50 +6248,5158 @@
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="inlineStr">
         <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n"/>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n"/>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n"/>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n"/>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n"/>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n"/>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n"/>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
           <t>clap</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n"/>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n"/>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n"/>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n"/>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n"/>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n"/>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n"/>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n"/>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n"/>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n"/>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n"/>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n"/>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n"/>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n"/>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n"/>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n"/>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n"/>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n"/>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n"/>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n"/>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n"/>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n"/>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n"/>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n"/>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n"/>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n"/>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n"/>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n"/>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n"/>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n"/>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n"/>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n"/>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n"/>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n"/>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n"/>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n"/>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n"/>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n"/>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n"/>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n"/>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n"/>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n"/>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n"/>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n"/>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n"/>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n"/>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n"/>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n"/>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n"/>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n"/>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n"/>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n"/>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n"/>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n"/>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n"/>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n"/>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n"/>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n"/>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n"/>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n"/>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n"/>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n"/>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n"/>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n"/>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n"/>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n"/>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n"/>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n"/>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-EnergyBased</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n"/>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Entropy</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n"/>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-KLMatching</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n"/>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-LogitNorm</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n"/>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-Mahalanobis</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n"/>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxLogit</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n"/>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-MaxSoftmax</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n"/>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-OpenMax</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n"/>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B-TemperatureScaling</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n"/>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n"/>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n"/>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -6319,21 +11407,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A89:A105"/>
+    <mergeCell ref="A106:A122"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A76:A84"/>
-    <mergeCell ref="A94:A102"/>
-    <mergeCell ref="A103:A111"/>
-    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="A123:A139"/>
+    <mergeCell ref="A21:A37"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A4:A12"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A31:A39"/>
-    <mergeCell ref="A49:A57"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="A85:A93"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="A67:A75"/>
+    <mergeCell ref="A38:A54"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A157:A173"/>
+    <mergeCell ref="A174:A190"/>
+    <mergeCell ref="A191:A207"/>
+    <mergeCell ref="A55:A71"/>
+    <mergeCell ref="A140:A156"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
